--- a/test/fixtures/files/upload_single_page/03_combo_update_samples_spreadsheet.xlsx
+++ b/test/fixtures/files/upload_single_page/03_combo_update_samples_spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kevin.depelseneer/dev/projects/seek/test/fixtures/files/upload_single_page/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4122E45E-2185-FD47-BD20-07A663C50787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3680872D-FA33-F44D-AE80-9E3005F1A2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample Type Metadata" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
   <si>
     <t>Study:</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>Title:</t>
+  </si>
+  <si>
+    <t>Bramley</t>
   </si>
 </sst>
 </file>
@@ -849,7 +852,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" t="s">
